--- a/Lab_4/data/partB/param_optimization_process/v200_k10_s150_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v200_k10_s150_results.xlsx
@@ -518,34 +518,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="n">
         <v>3</v>
       </c>
-      <c r="D2" t="n">
-        <v>1</v>
-      </c>
-      <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>11</v>
-      </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -554,13 +554,13 @@
         <v>8</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
       </c>
       <c r="P2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -570,49 +570,49 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>55</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>11</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
         <v>0</v>
-      </c>
-      <c r="C3" t="n">
-        <v>52</v>
-      </c>
-      <c r="D3" t="n">
-        <v>4</v>
-      </c>
-      <c r="E3" t="n">
-        <v>15</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" t="n">
-        <v>2</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2</v>
       </c>
       <c r="I3" t="n">
         <v>1</v>
       </c>
       <c r="J3" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,16 +646,16 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
+        <v>2</v>
+      </c>
+      <c r="M4" t="n">
         <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>1</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -674,49 +674,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>1</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8</v>
+      </c>
+      <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
-      <c r="J5" t="n">
-        <v>5</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5" t="n">
         <v>1</v>
       </c>
       <c r="N5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -729,46 +729,46 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="G6" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H6" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J6" t="n">
+        <v>3</v>
+      </c>
+      <c r="K6" t="n">
         <v>2</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="N6" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="O6" t="n">
         <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7">
@@ -778,7 +778,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -790,37 +790,37 @@
         <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G7" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>2</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
         <v>4</v>
       </c>
-      <c r="I7" t="n">
-        <v>3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>8</v>
-      </c>
       <c r="N7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -839,40 +839,40 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G8" t="n">
+        <v>12</v>
+      </c>
+      <c r="H8" t="n">
         <v>6</v>
       </c>
-      <c r="G8" t="n">
-        <v>15</v>
-      </c>
-      <c r="H8" t="n">
-        <v>16</v>
-      </c>
       <c r="I8" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P8" t="n">
         <v>2</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -882,10 +882,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
@@ -894,37 +894,37 @@
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O9" t="n">
         <v>2</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -934,16 +934,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -958,22 +958,22 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -998,37 +998,37 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="H11" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
         <v>1</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1041,16 +1041,16 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1062,25 +1062,25 @@
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
@@ -1102,37 +1102,37 @@
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G13" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1145,16 +1145,16 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="G14" t="n">
         <v>7</v>
@@ -1163,28 +1163,28 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N14" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15">
@@ -1197,13 +1197,13 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
         <v>1</v>
-      </c>
-      <c r="D15" t="n">
-        <v>6</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>7</v>
@@ -1218,7 +1218,7 @@
         <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
@@ -1227,13 +1227,13 @@
         <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1246,49 +1246,49 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
         <v>2</v>
-      </c>
-      <c r="C16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>2</v>
       </c>
       <c r="F16" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G16" t="n">
         <v>9</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>48</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1692,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1726,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1811,7 +1811,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2032,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2389,7 +2389,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2695,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2865,7 +2865,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3154,7 +3154,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3205,7 +3205,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3375,7 +3375,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3392,7 +3392,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3664,7 +3664,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3732,7 +3732,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3851,7 +3851,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -4208,7 +4208,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -4276,7 +4276,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4344,7 +4344,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4429,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6571,7 +6571,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6741,7 +6741,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6826,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7251,7 +7251,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7319,7 +7319,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7404,7 +7404,7 @@
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -7676,7 +7676,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7761,7 +7761,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7863,7 +7863,7 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7948,7 +7948,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -8305,7 +8305,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8339,7 +8339,7 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8356,7 +8356,7 @@
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8407,7 +8407,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8526,7 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -8611,7 +8611,7 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8866,7 +8866,7 @@
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9104,7 +9104,7 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9223,7 +9223,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -9342,7 +9342,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9444,7 +9444,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9682,7 +9682,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9716,7 +9716,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9818,7 +9818,7 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9835,7 +9835,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9954,7 +9954,7 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10056,7 +10056,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10073,7 +10073,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -10175,7 +10175,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10311,7 +10311,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10430,7 +10430,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10685,7 +10685,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10770,7 +10770,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10889,7 +10889,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11127,7 +11127,7 @@
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11263,7 +11263,7 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11297,7 +11297,7 @@
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -11365,7 +11365,7 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11603,7 +11603,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11705,7 +11705,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11875,7 +11875,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11892,7 +11892,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12096,7 +12096,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12249,7 +12249,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12283,7 +12283,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12589,7 +12589,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12691,7 +12691,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12861,7 +12861,7 @@
       </c>
       <c r="C680" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="C681" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12895,7 +12895,7 @@
       </c>
       <c r="C682" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12929,7 +12929,7 @@
       </c>
       <c r="C684" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12946,7 +12946,7 @@
       </c>
       <c r="C685" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13065,7 +13065,7 @@
       </c>
       <c r="C692" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="C693" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13099,7 +13099,7 @@
       </c>
       <c r="C694" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13133,7 +13133,7 @@
       </c>
       <c r="C696" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13507,7 +13507,7 @@
       </c>
       <c r="C718" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="C729" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13762,7 +13762,7 @@
       </c>
       <c r="C733" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13779,7 +13779,7 @@
       </c>
       <c r="C734" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13915,7 +13915,7 @@
       </c>
       <c r="C742" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="C747" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14051,7 +14051,7 @@
       </c>
       <c r="C750" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14068,7 +14068,7 @@
       </c>
       <c r="C751" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14085,7 +14085,7 @@
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14119,7 +14119,7 @@
       </c>
       <c r="C754" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -14187,7 +14187,7 @@
       </c>
       <c r="C758" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14255,7 +14255,7 @@
       </c>
       <c r="C762" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="C764" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="C765" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14323,7 +14323,7 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14340,7 +14340,7 @@
       </c>
       <c r="C767" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14357,7 +14357,7 @@
       </c>
       <c r="C768" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14425,7 +14425,7 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14476,7 +14476,7 @@
       </c>
       <c r="C775" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14544,7 +14544,7 @@
       </c>
       <c r="C779" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -14578,7 +14578,7 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -14595,7 +14595,7 @@
       </c>
       <c r="C782" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14646,7 +14646,7 @@
       </c>
       <c r="C785" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14663,7 +14663,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14901,7 +14901,7 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14935,7 +14935,7 @@
       </c>
       <c r="C802" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -14986,7 +14986,7 @@
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15088,7 +15088,7 @@
       </c>
       <c r="C811" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="C820" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -15309,7 +15309,7 @@
       </c>
       <c r="C824" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15479,7 +15479,7 @@
       </c>
       <c r="C834" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="C849" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15972,7 +15972,7 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15989,7 +15989,7 @@
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -16057,7 +16057,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16074,7 +16074,7 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16142,7 +16142,7 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16329,7 +16329,7 @@
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16397,7 +16397,7 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16669,7 +16669,7 @@
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16737,7 +16737,7 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16788,7 +16788,7 @@
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16805,7 +16805,7 @@
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -16924,7 +16924,7 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16941,7 +16941,7 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16992,7 +16992,7 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17026,7 +17026,7 @@
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17111,7 +17111,7 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17145,7 +17145,7 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -17162,7 +17162,7 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17298,7 +17298,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17315,7 +17315,7 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17400,7 +17400,7 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17451,7 +17451,7 @@
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17468,7 +17468,7 @@
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17519,7 +17519,7 @@
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17570,7 +17570,7 @@
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="C960" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17825,7 +17825,7 @@
       </c>
       <c r="C972" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17859,7 @@
       </c>
       <c r="C974" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17893,7 +17893,7 @@
       </c>
       <c r="C976" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17910,7 +17910,7 @@
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17927,7 +17927,7 @@
       </c>
       <c r="C978" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17978,7 +17978,7 @@
       </c>
       <c r="C981" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17995,7 +17995,7 @@
       </c>
       <c r="C982" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18012,7 +18012,7 @@
       </c>
       <c r="C983" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18029,7 +18029,7 @@
       </c>
       <c r="C984" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18046,7 +18046,7 @@
       </c>
       <c r="C985" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -18080,7 +18080,7 @@
       </c>
       <c r="C987" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18148,7 +18148,7 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18165,7 +18165,7 @@
       </c>
       <c r="C992" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18267,7 +18267,7 @@
       </c>
       <c r="C998" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -18335,7 +18335,7 @@
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18386,7 +18386,7 @@
       </c>
       <c r="C1005" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18403,7 +18403,7 @@
       </c>
       <c r="C1006" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18454,7 +18454,7 @@
       </c>
       <c r="C1009" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18471,7 +18471,7 @@
       </c>
       <c r="C1010" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18556,7 +18556,7 @@
       </c>
       <c r="C1015" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18624,7 @@
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18658,7 +18658,7 @@
       </c>
       <c r="C1021" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18777,7 +18777,7 @@
       </c>
       <c r="C1028" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18794,7 +18794,7 @@
       </c>
       <c r="C1029" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18913,7 +18913,7 @@
       </c>
       <c r="C1036" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18947,7 +18947,7 @@
       </c>
       <c r="C1038" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18964,7 +18964,7 @@
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19015,7 +19015,7 @@
       </c>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19049,7 +19049,7 @@
       </c>
       <c r="C1044" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19083,7 +19083,7 @@
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19134,7 +19134,7 @@
       </c>
       <c r="C1049" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19253,7 +19253,7 @@
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19270,7 +19270,7 @@
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19287,7 +19287,7 @@
       </c>
       <c r="C1058" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19321,7 +19321,7 @@
       </c>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19389,7 +19389,7 @@
       </c>
       <c r="C1064" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19423,7 +19423,7 @@
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19474,7 +19474,7 @@
       </c>
       <c r="C1069" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19491,7 +19491,7 @@
       </c>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19610,7 +19610,7 @@
       </c>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19661,7 +19661,7 @@
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19712,7 +19712,7 @@
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -19746,7 +19746,7 @@
       </c>
       <c r="C1085" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19780,7 +19780,7 @@
       </c>
       <c r="C1087" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="C1089" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19865,7 +19865,7 @@
       </c>
       <c r="C1092" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19899,7 +19899,7 @@
       </c>
       <c r="C1094" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19967,7 +19967,7 @@
       </c>
       <c r="C1098" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20018,7 +20018,7 @@
       </c>
       <c r="C1101" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20188,7 +20188,7 @@
       </c>
       <c r="C1111" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20239,7 +20239,7 @@
       </c>
       <c r="C1114" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20409,7 +20409,7 @@
       </c>
       <c r="C1124" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20426,7 +20426,7 @@
       </c>
       <c r="C1125" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="C1126" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20511,7 +20511,7 @@
       </c>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20647,7 +20647,7 @@
       </c>
       <c r="C1138" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20800,7 +20800,7 @@
       </c>
       <c r="C1147" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20851,7 +20851,7 @@
       </c>
       <c r="C1150" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="C1153" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20936,7 +20936,7 @@
       </c>
       <c r="C1155" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20970,7 +20970,7 @@
       </c>
       <c r="C1157" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21106,7 +21106,7 @@
       </c>
       <c r="C1165" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21293,7 +21293,7 @@
       </c>
       <c r="C1176" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -21412,7 +21412,7 @@
       </c>
       <c r="C1183" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21599,7 +21599,7 @@
       </c>
       <c r="C1194" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21616,7 +21616,7 @@
       </c>
       <c r="C1195" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21752,7 +21752,7 @@
       </c>
       <c r="C1203" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -21871,7 +21871,7 @@
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21888,7 +21888,7 @@
       </c>
       <c r="C1211" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21922,7 +21922,7 @@
       </c>
       <c r="C1213" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21939,7 +21939,7 @@
       </c>
       <c r="C1214" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21956,7 +21956,7 @@
       </c>
       <c r="C1215" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22007,7 +22007,7 @@
       </c>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22024,7 +22024,7 @@
       </c>
       <c r="C1219" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22041,7 +22041,7 @@
       </c>
       <c r="C1220" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22126,7 +22126,7 @@
       </c>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22143,7 +22143,7 @@
       </c>
       <c r="C1226" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22177,7 +22177,7 @@
       </c>
       <c r="C1228" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22245,7 +22245,7 @@
       </c>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="C1233" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22279,7 +22279,7 @@
       </c>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22296,7 +22296,7 @@
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22330,7 +22330,7 @@
       </c>
       <c r="C1237" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22381,7 +22381,7 @@
       </c>
       <c r="C1240" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22398,7 +22398,7 @@
       </c>
       <c r="C1241" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22432,7 @@
       </c>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22517,7 +22517,7 @@
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22789,7 +22789,7 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22840,7 +22840,7 @@
       </c>
       <c r="C1267" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="C1274" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22993,7 +22993,7 @@
       </c>
       <c r="C1276" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23010,7 +23010,7 @@
       </c>
       <c r="C1277" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23044,7 +23044,7 @@
       </c>
       <c r="C1279" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23265,7 +23265,7 @@
       </c>
       <c r="C1292" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="C1293" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23350,7 +23350,7 @@
       </c>
       <c r="C1297" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23401,7 +23401,7 @@
       </c>
       <c r="C1300" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23469,7 +23469,7 @@
       </c>
       <c r="C1304" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C1319" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -23758,7 +23758,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23843,7 +23843,7 @@
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23877,7 +23877,7 @@
       </c>
       <c r="C1328" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -24013,7 +24013,7 @@
       </c>
       <c r="C1336" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24234,7 +24234,7 @@
       </c>
       <c r="C1349" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24523,7 +24523,7 @@
       </c>
       <c r="C1366" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24557,7 +24557,7 @@
       </c>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24608,7 +24608,7 @@
       </c>
       <c r="C1371" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24795,7 +24795,7 @@
       </c>
       <c r="C1382" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24931,7 +24931,7 @@
       </c>
       <c r="C1390" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25067,7 +25067,7 @@
       </c>
       <c r="C1398" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25084,7 +25084,7 @@
       </c>
       <c r="C1399" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25118,7 +25118,7 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -25152,7 +25152,7 @@
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25169,7 +25169,7 @@
       </c>
       <c r="C1404" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25186,7 +25186,7 @@
       </c>
       <c r="C1405" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25220,7 +25220,7 @@
       </c>
       <c r="C1407" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25288,7 +25288,7 @@
       </c>
       <c r="C1411" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25356,7 +25356,7 @@
       </c>
       <c r="C1415" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25373,7 +25373,7 @@
       </c>
       <c r="C1416" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -25441,7 +25441,7 @@
       </c>
       <c r="C1420" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25492,7 +25492,7 @@
       </c>
       <c r="C1423" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="C1425" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -25543,7 +25543,7 @@
       </c>
       <c r="C1426" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25577,7 +25577,7 @@
       </c>
       <c r="C1428" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25594,7 +25594,7 @@
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25645,7 +25645,7 @@
       </c>
       <c r="C1432" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25696,7 +25696,7 @@
       </c>
       <c r="C1435" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25713,7 +25713,7 @@
       </c>
       <c r="C1436" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25747,7 +25747,7 @@
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -25764,7 +25764,7 @@
       </c>
       <c r="C1439" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C1448" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25968,7 +25968,7 @@
       </c>
       <c r="C1451" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26019,7 +26019,7 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26104,7 +26104,7 @@
       </c>
       <c r="C1459" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26121,7 +26121,7 @@
       </c>
       <c r="C1460" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26155,7 +26155,7 @@
       </c>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26240,7 @@
       </c>
       <c r="C1467" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26257,7 +26257,7 @@
       </c>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26325,7 +26325,7 @@
       </c>
       <c r="C1472" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26427,7 +26427,7 @@
       </c>
       <c r="C1478" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -26495,7 +26495,7 @@
       </c>
       <c r="C1482" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26546,7 +26546,7 @@
       </c>
       <c r="C1485" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -26563,7 +26563,7 @@
       </c>
       <c r="C1486" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26648,7 +26648,7 @@
       </c>
       <c r="C1491" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -26750,7 +26750,7 @@
       </c>
       <c r="C1497" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
